--- a/Data/fact_marketing.xlsx
+++ b/Data/fact_marketing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine Learning\Power BI\Projects\3\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analysis\Power BI\Projects\3- Andalusia\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DE6E4B-CF8B-4F42-AEFF-F01548772F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542CEC8F-834A-4191-8ADD-95E78ABCF30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56350C31-280B-463A-A3AA-DD87B752F566}"/>
   </bookViews>
@@ -39,43 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
-  <si>
-    <t>Date Key</t>
-  </si>
-  <si>
-    <t>BU Key</t>
-  </si>
-  <si>
-    <t>Baseline Revenue</t>
-  </si>
-  <si>
-    <t>Actual Revenue</t>
-  </si>
-  <si>
-    <t>Target Revenue</t>
-  </si>
-  <si>
-    <t>Actual Volume</t>
-  </si>
-  <si>
-    <t>Baseline Volume</t>
-  </si>
-  <si>
-    <t>Baseline RPP</t>
-  </si>
-  <si>
-    <t>Actual RPP</t>
-  </si>
-  <si>
-    <t>Target Volume</t>
-  </si>
-  <si>
-    <t>Target RPP</t>
-  </si>
-  <si>
-    <t>20250301</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>1</t>
   </si>
@@ -83,13 +47,40 @@
     <t>2</t>
   </si>
   <si>
-    <t>20250401</t>
-  </si>
-  <si>
-    <t>20250501</t>
-  </si>
-  <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>baseline_revenue</t>
+  </si>
+  <si>
+    <t>actual_revenue</t>
+  </si>
+  <si>
+    <t>target_revenue</t>
+  </si>
+  <si>
+    <t>actual_volume</t>
+  </si>
+  <si>
+    <t>baseline_volume</t>
+  </si>
+  <si>
+    <t>baseline_rpp</t>
+  </si>
+  <si>
+    <t>actual_rpp</t>
+  </si>
+  <si>
+    <t>target_volume</t>
+  </si>
+  <si>
+    <t>target_rpp</t>
+  </si>
+  <si>
+    <t>bu_key</t>
+  </si>
+  <si>
+    <t>date</t>
   </si>
 </sst>
 </file>
@@ -131,10 +122,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="15" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -474,352 +466,352 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>12111980.449999999</v>
+      </c>
+      <c r="B2" s="1">
+        <v>12152616.33</v>
+      </c>
+      <c r="C2" s="1">
+        <v>21154833.999999601</v>
+      </c>
+      <c r="D2" s="2">
+        <v>7647</v>
+      </c>
+      <c r="E2" s="2">
+        <v>8993</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1346.82313466029</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1589.20051392703</v>
+      </c>
+      <c r="H2" s="1">
+        <v>11917.0000000002</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1775.1811697574301</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K2" s="3">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>11683297.51</v>
+      </c>
+      <c r="B3" s="1">
+        <v>15184071.599999901</v>
+      </c>
+      <c r="C3" s="1">
+        <v>21248173.999999698</v>
+      </c>
+      <c r="D3" s="2">
+        <v>9442</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8722</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1339.5204666360901</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1608.14145308197</v>
+      </c>
+      <c r="H3" s="1">
+        <v>12245</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1735.2530828909501</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>12111980.449999999</v>
+      </c>
+      <c r="B4" s="1">
+        <v>5143092.97</v>
+      </c>
+      <c r="C4" s="1">
+        <v>21394563.000000101</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3531</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8993</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1346.82313466029</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1456.55422543189</v>
+      </c>
+      <c r="H4" s="1">
+        <v>12124.9999999998</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1764.5000412371401</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5976774.8600000003</v>
+      </c>
+      <c r="B5" s="1">
+        <v>4373517.4299999801</v>
+      </c>
+      <c r="C5" s="1">
+        <v>18670653.000000201</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3666</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5015</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1191.7796331007</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1192.9943889798101</v>
+      </c>
+      <c r="H5" s="1">
+        <v>10488.6000000001</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1780.09009782049</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K5" s="3">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5650457.71</v>
+      </c>
+      <c r="B6" s="1">
+        <v>7527882.9999999898</v>
+      </c>
+      <c r="C6" s="1">
+        <v>18908956.199999899</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4409</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4875</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1159.06824820513</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1707.39011113631</v>
+      </c>
+      <c r="H6" s="1">
+        <v>10547.9999999999</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1792.657963595</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5976774.8600000003</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2266731.6800000002</v>
+      </c>
+      <c r="C7" s="1">
+        <v>19745702.399999999</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1647</v>
+      </c>
+      <c r="E7" s="2">
+        <v>5015</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1191.7796331007</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1376.27910139648</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10574.9999999999</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1867.20590070923</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <v>45778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>10156243.32</v>
+      </c>
+      <c r="B8" s="1">
+        <v>8917910.5200000498</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9402229.3398331497</v>
+      </c>
+      <c r="D8" s="2">
+        <v>9135</v>
+      </c>
+      <c r="E8" s="2">
+        <v>10090</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1006.56524479683</v>
+      </c>
+      <c r="G8" s="1">
+        <v>976.235415435145</v>
+      </c>
+      <c r="H8" s="1">
+        <v>13426.739951633501</v>
+      </c>
+      <c r="I8" s="1">
+        <v>700.26152094271004</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1">
-        <v>12111980.449999999</v>
-      </c>
-      <c r="D2" s="1">
-        <v>12152616.33</v>
-      </c>
-      <c r="E2" s="1">
-        <v>21154833.999999601</v>
-      </c>
-      <c r="F2" s="2">
-        <v>7647</v>
-      </c>
-      <c r="G2" s="2">
-        <v>8993</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1346.82313466029</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1589.20051392703</v>
-      </c>
-      <c r="J2" s="1">
-        <v>11917.0000000002</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1775.1811697574301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1">
-        <v>5976774.8600000003</v>
-      </c>
-      <c r="D3" s="1">
-        <v>4373517.4299999801</v>
-      </c>
-      <c r="E3" s="1">
-        <v>18670653.000000201</v>
-      </c>
-      <c r="F3" s="2">
-        <v>3666</v>
-      </c>
-      <c r="G3" s="2">
-        <v>5015</v>
-      </c>
-      <c r="H3" s="1">
-        <v>1191.7796331007</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1192.9943889798101</v>
-      </c>
-      <c r="J3" s="1">
-        <v>10488.6000000001</v>
-      </c>
-      <c r="K3" s="1">
-        <v>1780.09009782049</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1">
-        <v>11683297.51</v>
-      </c>
-      <c r="D4" s="1">
-        <v>15184071.599999901</v>
-      </c>
-      <c r="E4" s="1">
-        <v>21248173.999999698</v>
-      </c>
-      <c r="F4" s="2">
-        <v>9442</v>
-      </c>
-      <c r="G4" s="2">
-        <v>8722</v>
-      </c>
-      <c r="H4" s="1">
-        <v>1339.5204666360901</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1608.14145308197</v>
-      </c>
-      <c r="J4" s="1">
-        <v>12245</v>
-      </c>
-      <c r="K4" s="1">
-        <v>1735.2530828909501</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1">
-        <v>12111980.449999999</v>
-      </c>
-      <c r="D5" s="1">
-        <v>5143092.97</v>
-      </c>
-      <c r="E5" s="1">
-        <v>21394563.000000101</v>
-      </c>
-      <c r="F5" s="2">
-        <v>3531</v>
-      </c>
-      <c r="G5" s="2">
-        <v>8993</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1346.82313466029</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1456.55422543189</v>
-      </c>
-      <c r="J5" s="1">
-        <v>12124.9999999998</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1764.5000412371401</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="1">
-        <v>5650457.71</v>
-      </c>
-      <c r="D6" s="1">
-        <v>7527882.9999999898</v>
-      </c>
-      <c r="E6" s="1">
-        <v>18908956.199999899</v>
-      </c>
-      <c r="F6" s="2">
-        <v>4409</v>
-      </c>
-      <c r="G6" s="2">
-        <v>4875</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1159.06824820513</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1707.39011113631</v>
-      </c>
-      <c r="J6" s="1">
-        <v>10547.9999999999</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1792.657963595</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5976774.8600000003</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2266731.6800000002</v>
-      </c>
-      <c r="E7" s="1">
-        <v>19745702.399999999</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1647</v>
-      </c>
-      <c r="G7" s="2">
-        <v>5015</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1191.7796331007</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1376.27910139648</v>
-      </c>
-      <c r="J7" s="1">
-        <v>10574.9999999999</v>
-      </c>
-      <c r="K7" s="1">
-        <v>1867.20590070923</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="K8" s="3">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>9663488.6699999999</v>
+      </c>
+      <c r="B9" s="1">
+        <v>11970838.84</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8931897.4299999699</v>
+      </c>
+      <c r="D9" s="2">
+        <v>11591</v>
+      </c>
+      <c r="E9" s="2">
+        <v>9695</v>
+      </c>
+      <c r="F9" s="1">
+        <v>996.74973388344495</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1032.77015270469</v>
+      </c>
+      <c r="H9" s="1">
+        <v>13056.9797900003</v>
+      </c>
+      <c r="I9" s="1">
+        <v>684.07070958633801</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K9" s="3">
+        <v>45748</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
         <v>10156243.32</v>
       </c>
-      <c r="D8" s="1">
-        <v>8917910.5200000498</v>
-      </c>
-      <c r="E8" s="1">
-        <v>9402229.3398331497</v>
-      </c>
-      <c r="F8" s="2">
-        <v>9135</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="B10" s="1">
+        <v>5079175.5699999901</v>
+      </c>
+      <c r="C10" s="1">
+        <v>11225932.8853001</v>
+      </c>
+      <c r="D10" s="2">
+        <v>3227</v>
+      </c>
+      <c r="E10" s="2">
         <v>10090</v>
       </c>
-      <c r="H8" s="1">
+      <c r="F10" s="1">
         <v>1006.56524479683</v>
       </c>
-      <c r="I8" s="1">
-        <v>976.235415435145</v>
-      </c>
-      <c r="J8" s="1">
-        <v>13426.739951633501</v>
-      </c>
-      <c r="K8" s="1">
-        <v>700.26152094271004</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="1">
-        <v>9663488.6699999999</v>
-      </c>
-      <c r="D9" s="1">
-        <v>11970838.84</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8931897.4299999699</v>
-      </c>
-      <c r="F9" s="2">
-        <v>11591</v>
-      </c>
-      <c r="G9" s="2">
-        <v>9695</v>
-      </c>
-      <c r="H9" s="1">
-        <v>996.74973388344495</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1032.77015270469</v>
-      </c>
-      <c r="J9" s="1">
-        <v>13056.9797900003</v>
-      </c>
-      <c r="K9" s="1">
-        <v>684.07070958633801</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="1">
-        <v>10156243.32</v>
-      </c>
-      <c r="D10" s="1">
-        <v>5079175.5699999901</v>
-      </c>
-      <c r="E10" s="1">
-        <v>11225932.8853001</v>
-      </c>
-      <c r="F10" s="2">
-        <v>3227</v>
-      </c>
-      <c r="G10" s="2">
-        <v>10090</v>
+      <c r="G10" s="1">
+        <v>1573.96206073752</v>
       </c>
       <c r="H10" s="1">
-        <v>1006.56524479683</v>
+        <v>16569.320000000102</v>
       </c>
       <c r="I10" s="1">
-        <v>1573.96206073752</v>
-      </c>
-      <c r="J10" s="1">
-        <v>16569.320000000102</v>
-      </c>
-      <c r="K10" s="1">
         <v>677.51319217083199</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3">
+        <v>45778</v>
       </c>
     </row>
   </sheetData>
